--- a/Audit_Activity_Log.xlsx
+++ b/Audit_Activity_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1405/06/23 - 10:29:08</t>
+          <t>1405/06/23 - 12:56:59</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1405/06/23 - 10:22:35</t>
+          <t>1405/06/23 - 10:29:08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -470,7 +470,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1405/06/23 - 10:03:50</t>
+          <t>1405/06/23 - 10:22:35</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -487,7 +487,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:54:24</t>
+          <t>1405/06/23 - 10:03:50</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -504,7 +504,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:37:17</t>
+          <t>1405/06/23 - 09:54:24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -521,41 +521,41 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:30:32</t>
+          <t>1405/06/23 - 09:37:17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>واحد برش و انبار</t>
+          <t>ورود به سیستم</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>پارت ۱-1 - فندقي  اسلیت شد. طاقه‌ها: 2</t>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:29:47</t>
+          <t>1405/06/23 - 09:30:32</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ورود به سیستم</t>
+          <t>واحد برش و انبار</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>پارت ۱-1 - فندقي  اسلیت شد. طاقه‌ها: 2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:24:06</t>
+          <t>1405/06/23 - 09:29:47</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:14:05</t>
+          <t>1405/06/23 - 09:24:06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -589,7 +589,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:10:17</t>
+          <t>1405/06/23 - 09:14:05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -606,7 +606,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1405/06/23 - 08:48:33</t>
+          <t>1405/06/23 - 09:10:17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -623,7 +623,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1405/06/23 - 22:06:41</t>
+          <t>1405/06/23 - 08:48:33</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -640,41 +640,41 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1405/06/23 - 22:05:44</t>
+          <t>1405/06/23 - 22:06:41</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>کارگاه دستگاه 1</t>
+          <t>ورود به سیستم</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>رول مادر با متراژ 2000.0 متر ثبت شد.</t>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1405/06/23 - 22:04:44</t>
+          <t>1405/06/23 - 22:05:44</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ورود به سیستم</t>
+          <t>کارگاه دستگاه 1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>رول مادر با متراژ 2000.0 متر ثبت شد.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1405/06/22 - 21:55:22</t>
+          <t>1405/06/23 - 22:04:44</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -691,7 +691,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1405/06/22 - 21:47:41</t>
+          <t>1405/06/22 - 21:55:22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -708,7 +708,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1405/06/22 - 17:06:19</t>
+          <t>1405/06/22 - 21:47:41</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -725,7 +725,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:59:10</t>
+          <t>1405/06/22 - 17:06:19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -742,7 +742,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:52:11</t>
+          <t>1405/06/22 - 16:59:10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -759,7 +759,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:49:08</t>
+          <t>1405/06/22 - 16:52:11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -776,7 +776,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:43:34</t>
+          <t>1405/06/22 - 16:49:08</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:32:13</t>
+          <t>1405/06/22 - 16:43:34</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -810,7 +810,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:03:51</t>
+          <t>1405/06/22 - 16:32:13</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -827,7 +827,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:36:36</t>
+          <t>1405/06/22 - 16:03:51</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -844,7 +844,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:30:04</t>
+          <t>1405/06/22 - 15:36:36</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -861,7 +861,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:26:02</t>
+          <t>1405/06/22 - 15:30:04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -878,7 +878,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:18:15</t>
+          <t>1405/06/22 - 15:26:02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -895,41 +895,41 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:15:07</t>
+          <t>1405/06/22 - 15:18:15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ثبت سفارش</t>
+          <t>ورود به سیستم</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>فاکتور ۱ برای مشتری مودب  ثبت شد.</t>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:14:25</t>
+          <t>1405/06/22 - 15:15:07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ورود به سیستم</t>
+          <t>ثبت سفارش</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>فاکتور ۱ برای مشتری مودب  ثبت شد.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:01:44</t>
+          <t>1405/06/22 - 15:14:25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1405/06/22 - 14:57:23</t>
+          <t>1405/06/22 - 15:01:44</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -963,7 +963,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1405/06/22 - 14:54:17</t>
+          <t>1405/06/22 - 14:57:23</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -980,7 +980,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1405/06/22 - 14:50:48</t>
+          <t>1405/06/22 - 14:54:17</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -997,7 +997,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1405/06/22 - 14:48:28</t>
+          <t>1405/06/22 - 14:50:48</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1014,15 +1014,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>1405/06/22 - 14:48:28</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ورود به سیستم</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>1405/06/22 - 14:45:00</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>ورود به سیستم</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ورود به سیستم</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>

--- a/Audit_Activity_Log.xlsx
+++ b/Audit_Activity_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,24 +436,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1405/06/23 - 12:56:59</t>
+          <t>1405/06/23 - 12:58:01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ورود به سیستم</t>
+          <t>مدیریت کاربران</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>دسترسی‌های کاربر Amin به‌روزرسانی شد.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1405/06/23 - 10:29:08</t>
+          <t>1405/06/23 - 12:56:59</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -470,7 +470,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1405/06/23 - 10:22:35</t>
+          <t>1405/06/23 - 10:29:08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -487,7 +487,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1405/06/23 - 10:03:50</t>
+          <t>1405/06/23 - 10:22:35</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -504,7 +504,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:54:24</t>
+          <t>1405/06/23 - 10:03:50</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -521,7 +521,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:37:17</t>
+          <t>1405/06/23 - 09:54:24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -538,41 +538,41 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:30:32</t>
+          <t>1405/06/23 - 09:37:17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>واحد برش و انبار</t>
+          <t>ورود به سیستم</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>پارت ۱-1 - فندقي  اسلیت شد. طاقه‌ها: 2</t>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:29:47</t>
+          <t>1405/06/23 - 09:30:32</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ورود به سیستم</t>
+          <t>واحد برش و انبار</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>پارت ۱-1 - فندقي  اسلیت شد. طاقه‌ها: 2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:24:06</t>
+          <t>1405/06/23 - 09:29:47</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -589,7 +589,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:14:05</t>
+          <t>1405/06/23 - 09:24:06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -606,7 +606,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:10:17</t>
+          <t>1405/06/23 - 09:14:05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -623,7 +623,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1405/06/23 - 08:48:33</t>
+          <t>1405/06/23 - 09:10:17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -640,7 +640,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1405/06/23 - 22:06:41</t>
+          <t>1405/06/23 - 08:48:33</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -657,41 +657,41 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1405/06/23 - 22:05:44</t>
+          <t>1405/06/23 - 22:06:41</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>کارگاه دستگاه 1</t>
+          <t>ورود به سیستم</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>رول مادر با متراژ 2000.0 متر ثبت شد.</t>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1405/06/23 - 22:04:44</t>
+          <t>1405/06/23 - 22:05:44</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ورود به سیستم</t>
+          <t>کارگاه دستگاه 1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>رول مادر با متراژ 2000.0 متر ثبت شد.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1405/06/22 - 21:55:22</t>
+          <t>1405/06/23 - 22:04:44</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -708,7 +708,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1405/06/22 - 21:47:41</t>
+          <t>1405/06/22 - 21:55:22</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -725,7 +725,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1405/06/22 - 17:06:19</t>
+          <t>1405/06/22 - 21:47:41</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -742,7 +742,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:59:10</t>
+          <t>1405/06/22 - 17:06:19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -759,7 +759,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:52:11</t>
+          <t>1405/06/22 - 16:59:10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -776,7 +776,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:49:08</t>
+          <t>1405/06/22 - 16:52:11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:43:34</t>
+          <t>1405/06/22 - 16:49:08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -810,7 +810,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:32:13</t>
+          <t>1405/06/22 - 16:43:34</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -827,7 +827,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:03:51</t>
+          <t>1405/06/22 - 16:32:13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -844,7 +844,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:36:36</t>
+          <t>1405/06/22 - 16:03:51</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -861,7 +861,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:30:04</t>
+          <t>1405/06/22 - 15:36:36</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -878,7 +878,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:26:02</t>
+          <t>1405/06/22 - 15:30:04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -895,7 +895,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:18:15</t>
+          <t>1405/06/22 - 15:26:02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -912,41 +912,41 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:15:07</t>
+          <t>1405/06/22 - 15:18:15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ثبت سفارش</t>
+          <t>ورود به سیستم</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>فاکتور ۱ برای مشتری مودب  ثبت شد.</t>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:14:25</t>
+          <t>1405/06/22 - 15:15:07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ورود به سیستم</t>
+          <t>ثبت سفارش</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>فاکتور ۱ برای مشتری مودب  ثبت شد.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:01:44</t>
+          <t>1405/06/22 - 15:14:25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -963,7 +963,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1405/06/22 - 14:57:23</t>
+          <t>1405/06/22 - 15:01:44</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -980,7 +980,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1405/06/22 - 14:54:17</t>
+          <t>1405/06/22 - 14:57:23</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -997,7 +997,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1405/06/22 - 14:50:48</t>
+          <t>1405/06/22 - 14:54:17</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1405/06/22 - 14:48:28</t>
+          <t>1405/06/22 - 14:50:48</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1031,15 +1031,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>1405/06/22 - 14:48:28</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ورود به سیستم</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>1405/06/22 - 14:45:00</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>ورود به سیستم</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ورود به سیستم</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
         <is>
           <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>

--- a/Audit_Activity_Log.xlsx
+++ b/Audit_Activity_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,41 +436,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1405/06/23 - 12:58:01</t>
+          <t>1405/06/23 - 12:58:14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>مدیریت کاربران</t>
+          <t>خروج</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>دسترسی‌های کاربر Amin به‌روزرسانی شد.</t>
+          <t>کاربر [مدیرعامل محترم] خارج شد.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1405/06/23 - 12:56:59</t>
+          <t>1405/06/23 - 12:58:01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ورود به سیستم</t>
+          <t>مدیریت کاربران</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>دسترسی‌های کاربر Amin به‌روزرسانی شد.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1405/06/23 - 10:29:08</t>
+          <t>1405/06/23 - 12:56:59</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -487,7 +487,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1405/06/23 - 10:22:35</t>
+          <t>1405/06/23 - 10:29:08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -504,7 +504,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1405/06/23 - 10:03:50</t>
+          <t>1405/06/23 - 10:22:35</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -521,7 +521,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:54:24</t>
+          <t>1405/06/23 - 10:03:50</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -538,7 +538,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:37:17</t>
+          <t>1405/06/23 - 09:54:24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -555,41 +555,41 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:30:32</t>
+          <t>1405/06/23 - 09:37:17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>واحد برش و انبار</t>
+          <t>ورود به سیستم</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>پارت ۱-1 - فندقي  اسلیت شد. طاقه‌ها: 2</t>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:29:47</t>
+          <t>1405/06/23 - 09:30:32</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ورود به سیستم</t>
+          <t>واحد برش و انبار</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>پارت ۱-1 - فندقي  اسلیت شد. طاقه‌ها: 2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:24:06</t>
+          <t>1405/06/23 - 09:29:47</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -606,7 +606,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:14:05</t>
+          <t>1405/06/23 - 09:24:06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -623,7 +623,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:10:17</t>
+          <t>1405/06/23 - 09:14:05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -640,7 +640,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1405/06/23 - 08:48:33</t>
+          <t>1405/06/23 - 09:10:17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -657,7 +657,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1405/06/23 - 22:06:41</t>
+          <t>1405/06/23 - 08:48:33</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -674,41 +674,41 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1405/06/23 - 22:05:44</t>
+          <t>1405/06/23 - 22:06:41</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>کارگاه دستگاه 1</t>
+          <t>ورود به سیستم</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>رول مادر با متراژ 2000.0 متر ثبت شد.</t>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1405/06/23 - 22:04:44</t>
+          <t>1405/06/23 - 22:05:44</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ورود به سیستم</t>
+          <t>کارگاه دستگاه 1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>رول مادر با متراژ 2000.0 متر ثبت شد.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1405/06/22 - 21:55:22</t>
+          <t>1405/06/23 - 22:04:44</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -725,7 +725,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1405/06/22 - 21:47:41</t>
+          <t>1405/06/22 - 21:55:22</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -742,7 +742,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1405/06/22 - 17:06:19</t>
+          <t>1405/06/22 - 21:47:41</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -759,7 +759,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:59:10</t>
+          <t>1405/06/22 - 17:06:19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -776,7 +776,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:52:11</t>
+          <t>1405/06/22 - 16:59:10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:49:08</t>
+          <t>1405/06/22 - 16:52:11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -810,7 +810,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:43:34</t>
+          <t>1405/06/22 - 16:49:08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -827,7 +827,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:32:13</t>
+          <t>1405/06/22 - 16:43:34</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -844,7 +844,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:03:51</t>
+          <t>1405/06/22 - 16:32:13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -861,7 +861,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:36:36</t>
+          <t>1405/06/22 - 16:03:51</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -878,7 +878,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:30:04</t>
+          <t>1405/06/22 - 15:36:36</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -895,7 +895,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:26:02</t>
+          <t>1405/06/22 - 15:30:04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:18:15</t>
+          <t>1405/06/22 - 15:26:02</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -929,41 +929,41 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:15:07</t>
+          <t>1405/06/22 - 15:18:15</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ثبت سفارش</t>
+          <t>ورود به سیستم</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>فاکتور ۱ برای مشتری مودب  ثبت شد.</t>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:14:25</t>
+          <t>1405/06/22 - 15:15:07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ورود به سیستم</t>
+          <t>ثبت سفارش</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>فاکتور ۱ برای مشتری مودب  ثبت شد.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:01:44</t>
+          <t>1405/06/22 - 15:14:25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -980,7 +980,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1405/06/22 - 14:57:23</t>
+          <t>1405/06/22 - 15:01:44</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -997,7 +997,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1405/06/22 - 14:54:17</t>
+          <t>1405/06/22 - 14:57:23</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1405/06/22 - 14:50:48</t>
+          <t>1405/06/22 - 14:54:17</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1031,7 +1031,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1405/06/22 - 14:48:28</t>
+          <t>1405/06/22 - 14:50:48</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1048,15 +1048,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>1405/06/22 - 14:48:28</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ورود به سیستم</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>1405/06/22 - 14:45:00</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>ورود به سیستم</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ورود به سیستم</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
         <is>
           <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>

--- a/Audit_Activity_Log.xlsx
+++ b/Audit_Activity_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,58 +436,58 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1405/06/23 - 12:58:14</t>
+          <t>1405/06/23 - 12:58:36</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>خروج</t>
+          <t>ورود به سیستم</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] خارج شد.</t>
+          <t>کاربر [اقای مودب ] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1405/06/23 - 12:58:01</t>
+          <t>1405/06/23 - 12:58:14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>مدیریت کاربران</t>
+          <t>خروج</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>دسترسی‌های کاربر Amin به‌روزرسانی شد.</t>
+          <t>کاربر [مدیرعامل محترم] خارج شد.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1405/06/23 - 12:56:59</t>
+          <t>1405/06/23 - 12:58:01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ورود به سیستم</t>
+          <t>مدیریت کاربران</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>دسترسی‌های کاربر Amin به‌روزرسانی شد.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1405/06/23 - 10:29:08</t>
+          <t>1405/06/23 - 12:56:59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -504,7 +504,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1405/06/23 - 10:22:35</t>
+          <t>1405/06/23 - 10:29:08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -521,7 +521,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1405/06/23 - 10:03:50</t>
+          <t>1405/06/23 - 10:22:35</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -538,7 +538,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:54:24</t>
+          <t>1405/06/23 - 10:03:50</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:37:17</t>
+          <t>1405/06/23 - 09:54:24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -572,41 +572,41 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:30:32</t>
+          <t>1405/06/23 - 09:37:17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>واحد برش و انبار</t>
+          <t>ورود به سیستم</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>پارت ۱-1 - فندقي  اسلیت شد. طاقه‌ها: 2</t>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:29:47</t>
+          <t>1405/06/23 - 09:30:32</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ورود به سیستم</t>
+          <t>واحد برش و انبار</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>پارت ۱-1 - فندقي  اسلیت شد. طاقه‌ها: 2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:24:06</t>
+          <t>1405/06/23 - 09:29:47</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -623,7 +623,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:14:05</t>
+          <t>1405/06/23 - 09:24:06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -640,7 +640,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:10:17</t>
+          <t>1405/06/23 - 09:14:05</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -657,7 +657,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1405/06/23 - 08:48:33</t>
+          <t>1405/06/23 - 09:10:17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -674,7 +674,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1405/06/23 - 22:06:41</t>
+          <t>1405/06/23 - 08:48:33</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -691,41 +691,41 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1405/06/23 - 22:05:44</t>
+          <t>1405/06/23 - 22:06:41</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>کارگاه دستگاه 1</t>
+          <t>ورود به سیستم</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>رول مادر با متراژ 2000.0 متر ثبت شد.</t>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1405/06/23 - 22:04:44</t>
+          <t>1405/06/23 - 22:05:44</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ورود به سیستم</t>
+          <t>کارگاه دستگاه 1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>رول مادر با متراژ 2000.0 متر ثبت شد.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1405/06/22 - 21:55:22</t>
+          <t>1405/06/23 - 22:04:44</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -742,7 +742,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1405/06/22 - 21:47:41</t>
+          <t>1405/06/22 - 21:55:22</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -759,7 +759,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1405/06/22 - 17:06:19</t>
+          <t>1405/06/22 - 21:47:41</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -776,7 +776,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:59:10</t>
+          <t>1405/06/22 - 17:06:19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:52:11</t>
+          <t>1405/06/22 - 16:59:10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -810,7 +810,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:49:08</t>
+          <t>1405/06/22 - 16:52:11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -827,7 +827,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:43:34</t>
+          <t>1405/06/22 - 16:49:08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -844,7 +844,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:32:13</t>
+          <t>1405/06/22 - 16:43:34</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -861,7 +861,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:03:51</t>
+          <t>1405/06/22 - 16:32:13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -878,7 +878,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:36:36</t>
+          <t>1405/06/22 - 16:03:51</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -895,7 +895,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:30:04</t>
+          <t>1405/06/22 - 15:36:36</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:26:02</t>
+          <t>1405/06/22 - 15:30:04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -929,7 +929,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:18:15</t>
+          <t>1405/06/22 - 15:26:02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -946,41 +946,41 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:15:07</t>
+          <t>1405/06/22 - 15:18:15</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ثبت سفارش</t>
+          <t>ورود به سیستم</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>فاکتور ۱ برای مشتری مودب  ثبت شد.</t>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:14:25</t>
+          <t>1405/06/22 - 15:15:07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ورود به سیستم</t>
+          <t>ثبت سفارش</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>فاکتور ۱ برای مشتری مودب  ثبت شد.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:01:44</t>
+          <t>1405/06/22 - 15:14:25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -997,7 +997,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1405/06/22 - 14:57:23</t>
+          <t>1405/06/22 - 15:01:44</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1405/06/22 - 14:54:17</t>
+          <t>1405/06/22 - 14:57:23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1031,7 +1031,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1405/06/22 - 14:50:48</t>
+          <t>1405/06/22 - 14:54:17</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1405/06/22 - 14:48:28</t>
+          <t>1405/06/22 - 14:50:48</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1065,15 +1065,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>1405/06/22 - 14:48:28</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ورود به سیستم</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>1405/06/22 - 14:45:00</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>ورود به سیستم</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ورود به سیستم</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
         <is>
           <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>

--- a/Audit_Activity_Log.xlsx
+++ b/Audit_Activity_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1405/06/23 - 12:58:36</t>
+          <t>1405/06/23 - 13:14:18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -446,65 +446,65 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>کاربر [اقای مودب ] وارد شد.</t>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1405/06/23 - 12:58:14</t>
+          <t>1405/06/23 - 12:58:36</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>خروج</t>
+          <t>ورود به سیستم</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] خارج شد.</t>
+          <t>کاربر [اقای مودب ] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1405/06/23 - 12:58:01</t>
+          <t>1405/06/23 - 12:58:14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>مدیریت کاربران</t>
+          <t>خروج</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>دسترسی‌های کاربر Amin به‌روزرسانی شد.</t>
+          <t>کاربر [مدیرعامل محترم] خارج شد.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1405/06/23 - 12:56:59</t>
+          <t>1405/06/23 - 12:58:01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ورود به سیستم</t>
+          <t>مدیریت کاربران</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>دسترسی‌های کاربر Amin به‌روزرسانی شد.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1405/06/23 - 10:29:08</t>
+          <t>1405/06/23 - 12:56:59</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -521,7 +521,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1405/06/23 - 10:22:35</t>
+          <t>1405/06/23 - 10:29:08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -538,7 +538,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1405/06/23 - 10:03:50</t>
+          <t>1405/06/23 - 10:22:35</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:54:24</t>
+          <t>1405/06/23 - 10:03:50</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:37:17</t>
+          <t>1405/06/23 - 09:54:24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -589,41 +589,41 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:30:32</t>
+          <t>1405/06/23 - 09:37:17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>واحد برش و انبار</t>
+          <t>ورود به سیستم</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>پارت ۱-1 - فندقي  اسلیت شد. طاقه‌ها: 2</t>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:29:47</t>
+          <t>1405/06/23 - 09:30:32</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ورود به سیستم</t>
+          <t>واحد برش و انبار</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>پارت ۱-1 - فندقي  اسلیت شد. طاقه‌ها: 2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:24:06</t>
+          <t>1405/06/23 - 09:29:47</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -640,7 +640,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:14:05</t>
+          <t>1405/06/23 - 09:24:06</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -657,7 +657,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:10:17</t>
+          <t>1405/06/23 - 09:14:05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -674,7 +674,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1405/06/23 - 08:48:33</t>
+          <t>1405/06/23 - 09:10:17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -691,7 +691,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1405/06/23 - 22:06:41</t>
+          <t>1405/06/23 - 08:48:33</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -708,41 +708,41 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1405/06/23 - 22:05:44</t>
+          <t>1405/06/23 - 22:06:41</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>کارگاه دستگاه 1</t>
+          <t>ورود به سیستم</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>رول مادر با متراژ 2000.0 متر ثبت شد.</t>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1405/06/23 - 22:04:44</t>
+          <t>1405/06/23 - 22:05:44</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ورود به سیستم</t>
+          <t>کارگاه دستگاه 1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>رول مادر با متراژ 2000.0 متر ثبت شد.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1405/06/22 - 21:55:22</t>
+          <t>1405/06/23 - 22:04:44</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -759,7 +759,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1405/06/22 - 21:47:41</t>
+          <t>1405/06/22 - 21:55:22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -776,7 +776,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1405/06/22 - 17:06:19</t>
+          <t>1405/06/22 - 21:47:41</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:59:10</t>
+          <t>1405/06/22 - 17:06:19</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -810,7 +810,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:52:11</t>
+          <t>1405/06/22 - 16:59:10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -827,7 +827,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:49:08</t>
+          <t>1405/06/22 - 16:52:11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -844,7 +844,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:43:34</t>
+          <t>1405/06/22 - 16:49:08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -861,7 +861,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:32:13</t>
+          <t>1405/06/22 - 16:43:34</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -878,7 +878,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:03:51</t>
+          <t>1405/06/22 - 16:32:13</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -895,7 +895,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:36:36</t>
+          <t>1405/06/22 - 16:03:51</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:30:04</t>
+          <t>1405/06/22 - 15:36:36</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -929,7 +929,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:26:02</t>
+          <t>1405/06/22 - 15:30:04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:18:15</t>
+          <t>1405/06/22 - 15:26:02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -963,41 +963,41 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:15:07</t>
+          <t>1405/06/22 - 15:18:15</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ثبت سفارش</t>
+          <t>ورود به سیستم</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>فاکتور ۱ برای مشتری مودب  ثبت شد.</t>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:14:25</t>
+          <t>1405/06/22 - 15:15:07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ورود به سیستم</t>
+          <t>ثبت سفارش</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>فاکتور ۱ برای مشتری مودب  ثبت شد.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:01:44</t>
+          <t>1405/06/22 - 15:14:25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1405/06/22 - 14:57:23</t>
+          <t>1405/06/22 - 15:01:44</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1031,7 +1031,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1405/06/22 - 14:54:17</t>
+          <t>1405/06/22 - 14:57:23</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1405/06/22 - 14:50:48</t>
+          <t>1405/06/22 - 14:54:17</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1065,7 +1065,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1405/06/22 - 14:48:28</t>
+          <t>1405/06/22 - 14:50:48</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1082,15 +1082,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>1405/06/22 - 14:48:28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ورود به سیستم</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>1405/06/22 - 14:45:00</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>ورود به سیستم</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ورود به سیستم</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
         <is>
           <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>

--- a/Audit_Activity_Log.xlsx
+++ b/Audit_Activity_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1405/06/23 - 13:14:18</t>
+          <t>1405/06/23 - 15:53:52</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -446,14 +446,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>کاربر [اقای مودب ] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1405/06/23 - 12:58:36</t>
+          <t>1405/06/23 - 13:14:18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -463,65 +463,65 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>کاربر [اقای مودب ] وارد شد.</t>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1405/06/23 - 12:58:14</t>
+          <t>1405/06/23 - 12:58:36</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>خروج</t>
+          <t>ورود به سیستم</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] خارج شد.</t>
+          <t>کاربر [اقای مودب ] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1405/06/23 - 12:58:01</t>
+          <t>1405/06/23 - 12:58:14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>مدیریت کاربران</t>
+          <t>خروج</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>دسترسی‌های کاربر Amin به‌روزرسانی شد.</t>
+          <t>کاربر [مدیرعامل محترم] خارج شد.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1405/06/23 - 12:56:59</t>
+          <t>1405/06/23 - 12:58:01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ورود به سیستم</t>
+          <t>مدیریت کاربران</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>دسترسی‌های کاربر Amin به‌روزرسانی شد.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1405/06/23 - 10:29:08</t>
+          <t>1405/06/23 - 12:56:59</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -538,7 +538,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1405/06/23 - 10:22:35</t>
+          <t>1405/06/23 - 10:29:08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1405/06/23 - 10:03:50</t>
+          <t>1405/06/23 - 10:22:35</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:54:24</t>
+          <t>1405/06/23 - 10:03:50</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -589,7 +589,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:37:17</t>
+          <t>1405/06/23 - 09:54:24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -606,41 +606,41 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:30:32</t>
+          <t>1405/06/23 - 09:37:17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>واحد برش و انبار</t>
+          <t>ورود به سیستم</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>پارت ۱-1 - فندقي  اسلیت شد. طاقه‌ها: 2</t>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:29:47</t>
+          <t>1405/06/23 - 09:30:32</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ورود به سیستم</t>
+          <t>واحد برش و انبار</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>پارت ۱-1 - فندقي  اسلیت شد. طاقه‌ها: 2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:24:06</t>
+          <t>1405/06/23 - 09:29:47</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -657,7 +657,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:14:05</t>
+          <t>1405/06/23 - 09:24:06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -674,7 +674,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:10:17</t>
+          <t>1405/06/23 - 09:14:05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -691,7 +691,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1405/06/23 - 08:48:33</t>
+          <t>1405/06/23 - 09:10:17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -708,7 +708,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1405/06/23 - 22:06:41</t>
+          <t>1405/06/23 - 08:48:33</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -725,41 +725,41 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1405/06/23 - 22:05:44</t>
+          <t>1405/06/23 - 22:06:41</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>کارگاه دستگاه 1</t>
+          <t>ورود به سیستم</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>رول مادر با متراژ 2000.0 متر ثبت شد.</t>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1405/06/23 - 22:04:44</t>
+          <t>1405/06/23 - 22:05:44</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ورود به سیستم</t>
+          <t>کارگاه دستگاه 1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>رول مادر با متراژ 2000.0 متر ثبت شد.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1405/06/22 - 21:55:22</t>
+          <t>1405/06/23 - 22:04:44</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -776,7 +776,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1405/06/22 - 21:47:41</t>
+          <t>1405/06/22 - 21:55:22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1405/06/22 - 17:06:19</t>
+          <t>1405/06/22 - 21:47:41</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -810,7 +810,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:59:10</t>
+          <t>1405/06/22 - 17:06:19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -827,7 +827,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:52:11</t>
+          <t>1405/06/22 - 16:59:10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -844,7 +844,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:49:08</t>
+          <t>1405/06/22 - 16:52:11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -861,7 +861,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:43:34</t>
+          <t>1405/06/22 - 16:49:08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -878,7 +878,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:32:13</t>
+          <t>1405/06/22 - 16:43:34</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -895,7 +895,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:03:51</t>
+          <t>1405/06/22 - 16:32:13</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:36:36</t>
+          <t>1405/06/22 - 16:03:51</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -929,7 +929,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:30:04</t>
+          <t>1405/06/22 - 15:36:36</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:26:02</t>
+          <t>1405/06/22 - 15:30:04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -963,7 +963,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:18:15</t>
+          <t>1405/06/22 - 15:26:02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -980,41 +980,41 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:15:07</t>
+          <t>1405/06/22 - 15:18:15</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ثبت سفارش</t>
+          <t>ورود به سیستم</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>فاکتور ۱ برای مشتری مودب  ثبت شد.</t>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:14:25</t>
+          <t>1405/06/22 - 15:15:07</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ورود به سیستم</t>
+          <t>ثبت سفارش</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>فاکتور ۱ برای مشتری مودب  ثبت شد.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:01:44</t>
+          <t>1405/06/22 - 15:14:25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1031,7 +1031,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1405/06/22 - 14:57:23</t>
+          <t>1405/06/22 - 15:01:44</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1405/06/22 - 14:54:17</t>
+          <t>1405/06/22 - 14:57:23</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1065,7 +1065,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1405/06/22 - 14:50:48</t>
+          <t>1405/06/22 - 14:54:17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1082,7 +1082,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1405/06/22 - 14:48:28</t>
+          <t>1405/06/22 - 14:50:48</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1099,15 +1099,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>1405/06/22 - 14:48:28</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ورود به سیستم</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>1405/06/22 - 14:45:00</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>ورود به سیستم</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ورود به سیستم</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
         <is>
           <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>

--- a/Audit_Activity_Log.xlsx
+++ b/Audit_Activity_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1405/06/23 - 15:53:52</t>
+          <t>1405/06/26 - 11:48:02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1405/06/23 - 13:14:18</t>
+          <t>1405/06/23 - 15:53:52</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -463,14 +463,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>کاربر [اقای مودب ] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1405/06/23 - 12:58:36</t>
+          <t>1405/06/23 - 13:14:18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -480,65 +480,65 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>کاربر [اقای مودب ] وارد شد.</t>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1405/06/23 - 12:58:14</t>
+          <t>1405/06/23 - 12:58:36</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>خروج</t>
+          <t>ورود به سیستم</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] خارج شد.</t>
+          <t>کاربر [اقای مودب ] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1405/06/23 - 12:58:01</t>
+          <t>1405/06/23 - 12:58:14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>مدیریت کاربران</t>
+          <t>خروج</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>دسترسی‌های کاربر Amin به‌روزرسانی شد.</t>
+          <t>کاربر [مدیرعامل محترم] خارج شد.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1405/06/23 - 12:56:59</t>
+          <t>1405/06/23 - 12:58:01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ورود به سیستم</t>
+          <t>مدیریت کاربران</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>دسترسی‌های کاربر Amin به‌روزرسانی شد.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1405/06/23 - 10:29:08</t>
+          <t>1405/06/23 - 12:56:59</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1405/06/23 - 10:22:35</t>
+          <t>1405/06/23 - 10:29:08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1405/06/23 - 10:03:50</t>
+          <t>1405/06/23 - 10:22:35</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -589,7 +589,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:54:24</t>
+          <t>1405/06/23 - 10:03:50</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -606,7 +606,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:37:17</t>
+          <t>1405/06/23 - 09:54:24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -623,41 +623,41 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:30:32</t>
+          <t>1405/06/23 - 09:37:17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>واحد برش و انبار</t>
+          <t>ورود به سیستم</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>پارت ۱-1 - فندقي  اسلیت شد. طاقه‌ها: 2</t>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:29:47</t>
+          <t>1405/06/23 - 09:30:32</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ورود به سیستم</t>
+          <t>واحد برش و انبار</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>پارت ۱-1 - فندقي  اسلیت شد. طاقه‌ها: 2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:24:06</t>
+          <t>1405/06/23 - 09:29:47</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -674,7 +674,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:14:05</t>
+          <t>1405/06/23 - 09:24:06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -691,7 +691,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:10:17</t>
+          <t>1405/06/23 - 09:14:05</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -708,7 +708,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1405/06/23 - 08:48:33</t>
+          <t>1405/06/23 - 09:10:17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -725,7 +725,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1405/06/23 - 22:06:41</t>
+          <t>1405/06/23 - 08:48:33</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -742,41 +742,41 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1405/06/23 - 22:05:44</t>
+          <t>1405/06/23 - 22:06:41</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>کارگاه دستگاه 1</t>
+          <t>ورود به سیستم</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>رول مادر با متراژ 2000.0 متر ثبت شد.</t>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1405/06/23 - 22:04:44</t>
+          <t>1405/06/23 - 22:05:44</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ورود به سیستم</t>
+          <t>کارگاه دستگاه 1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>رول مادر با متراژ 2000.0 متر ثبت شد.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1405/06/22 - 21:55:22</t>
+          <t>1405/06/23 - 22:04:44</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1405/06/22 - 21:47:41</t>
+          <t>1405/06/22 - 21:55:22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -810,7 +810,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1405/06/22 - 17:06:19</t>
+          <t>1405/06/22 - 21:47:41</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -827,7 +827,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:59:10</t>
+          <t>1405/06/22 - 17:06:19</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -844,7 +844,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:52:11</t>
+          <t>1405/06/22 - 16:59:10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -861,7 +861,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:49:08</t>
+          <t>1405/06/22 - 16:52:11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -878,7 +878,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:43:34</t>
+          <t>1405/06/22 - 16:49:08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -895,7 +895,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:32:13</t>
+          <t>1405/06/22 - 16:43:34</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:03:51</t>
+          <t>1405/06/22 - 16:32:13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -929,7 +929,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:36:36</t>
+          <t>1405/06/22 - 16:03:51</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:30:04</t>
+          <t>1405/06/22 - 15:36:36</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -963,7 +963,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:26:02</t>
+          <t>1405/06/22 - 15:30:04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -980,7 +980,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:18:15</t>
+          <t>1405/06/22 - 15:26:02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -997,41 +997,41 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:15:07</t>
+          <t>1405/06/22 - 15:18:15</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ثبت سفارش</t>
+          <t>ورود به سیستم</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>فاکتور ۱ برای مشتری مودب  ثبت شد.</t>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:14:25</t>
+          <t>1405/06/22 - 15:15:07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ورود به سیستم</t>
+          <t>ثبت سفارش</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>فاکتور ۱ برای مشتری مودب  ثبت شد.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:01:44</t>
+          <t>1405/06/22 - 15:14:25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1405/06/22 - 14:57:23</t>
+          <t>1405/06/22 - 15:01:44</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1065,7 +1065,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1405/06/22 - 14:54:17</t>
+          <t>1405/06/22 - 14:57:23</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1082,7 +1082,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1405/06/22 - 14:50:48</t>
+          <t>1405/06/22 - 14:54:17</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1099,7 +1099,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1405/06/22 - 14:48:28</t>
+          <t>1405/06/22 - 14:50:48</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1116,15 +1116,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>1405/06/22 - 14:48:28</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ورود به سیستم</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>1405/06/22 - 14:45:00</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>ورود به سیستم</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ورود به سیستم</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
         <is>
           <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>

--- a/Audit_Activity_Log.xlsx
+++ b/Audit_Activity_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1405/06/26 - 11:48:02</t>
+          <t>1405/06/28 - 11:53:48</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1405/06/23 - 15:53:52</t>
+          <t>1405/06/26 - 11:48:02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -470,7 +470,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1405/06/23 - 13:14:18</t>
+          <t>1405/06/23 - 15:53:52</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -480,14 +480,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>کاربر [اقای مودب ] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1405/06/23 - 12:58:36</t>
+          <t>1405/06/23 - 13:14:18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -497,65 +497,65 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>کاربر [اقای مودب ] وارد شد.</t>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1405/06/23 - 12:58:14</t>
+          <t>1405/06/23 - 12:58:36</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>خروج</t>
+          <t>ورود به سیستم</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] خارج شد.</t>
+          <t>کاربر [اقای مودب ] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1405/06/23 - 12:58:01</t>
+          <t>1405/06/23 - 12:58:14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>مدیریت کاربران</t>
+          <t>خروج</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>دسترسی‌های کاربر Amin به‌روزرسانی شد.</t>
+          <t>کاربر [مدیرعامل محترم] خارج شد.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1405/06/23 - 12:56:59</t>
+          <t>1405/06/23 - 12:58:01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ورود به سیستم</t>
+          <t>مدیریت کاربران</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>دسترسی‌های کاربر Amin به‌روزرسانی شد.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1405/06/23 - 10:29:08</t>
+          <t>1405/06/23 - 12:56:59</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1405/06/23 - 10:22:35</t>
+          <t>1405/06/23 - 10:29:08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -589,7 +589,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1405/06/23 - 10:03:50</t>
+          <t>1405/06/23 - 10:22:35</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -606,7 +606,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:54:24</t>
+          <t>1405/06/23 - 10:03:50</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -623,7 +623,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:37:17</t>
+          <t>1405/06/23 - 09:54:24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -640,41 +640,41 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:30:32</t>
+          <t>1405/06/23 - 09:37:17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>واحد برش و انبار</t>
+          <t>ورود به سیستم</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>پارت ۱-1 - فندقي  اسلیت شد. طاقه‌ها: 2</t>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:29:47</t>
+          <t>1405/06/23 - 09:30:32</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ورود به سیستم</t>
+          <t>واحد برش و انبار</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>پارت ۱-1 - فندقي  اسلیت شد. طاقه‌ها: 2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:24:06</t>
+          <t>1405/06/23 - 09:29:47</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -691,7 +691,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:14:05</t>
+          <t>1405/06/23 - 09:24:06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -708,7 +708,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:10:17</t>
+          <t>1405/06/23 - 09:14:05</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -725,7 +725,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1405/06/23 - 08:48:33</t>
+          <t>1405/06/23 - 09:10:17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -742,7 +742,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1405/06/23 - 22:06:41</t>
+          <t>1405/06/23 - 08:48:33</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -759,41 +759,41 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1405/06/23 - 22:05:44</t>
+          <t>1405/06/23 - 22:06:41</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>کارگاه دستگاه 1</t>
+          <t>ورود به سیستم</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>رول مادر با متراژ 2000.0 متر ثبت شد.</t>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1405/06/23 - 22:04:44</t>
+          <t>1405/06/23 - 22:05:44</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ورود به سیستم</t>
+          <t>کارگاه دستگاه 1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>رول مادر با متراژ 2000.0 متر ثبت شد.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1405/06/22 - 21:55:22</t>
+          <t>1405/06/23 - 22:04:44</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -810,7 +810,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1405/06/22 - 21:47:41</t>
+          <t>1405/06/22 - 21:55:22</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -827,7 +827,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1405/06/22 - 17:06:19</t>
+          <t>1405/06/22 - 21:47:41</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -844,7 +844,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:59:10</t>
+          <t>1405/06/22 - 17:06:19</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -861,7 +861,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:52:11</t>
+          <t>1405/06/22 - 16:59:10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -878,7 +878,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:49:08</t>
+          <t>1405/06/22 - 16:52:11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -895,7 +895,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:43:34</t>
+          <t>1405/06/22 - 16:49:08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:32:13</t>
+          <t>1405/06/22 - 16:43:34</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -929,7 +929,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:03:51</t>
+          <t>1405/06/22 - 16:32:13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:36:36</t>
+          <t>1405/06/22 - 16:03:51</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -963,7 +963,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:30:04</t>
+          <t>1405/06/22 - 15:36:36</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -980,7 +980,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:26:02</t>
+          <t>1405/06/22 - 15:30:04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -997,7 +997,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:18:15</t>
+          <t>1405/06/22 - 15:26:02</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1014,41 +1014,41 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:15:07</t>
+          <t>1405/06/22 - 15:18:15</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ثبت سفارش</t>
+          <t>ورود به سیستم</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>فاکتور ۱ برای مشتری مودب  ثبت شد.</t>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:14:25</t>
+          <t>1405/06/22 - 15:15:07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ورود به سیستم</t>
+          <t>ثبت سفارش</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>فاکتور ۱ برای مشتری مودب  ثبت شد.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:01:44</t>
+          <t>1405/06/22 - 15:14:25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1065,7 +1065,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1405/06/22 - 14:57:23</t>
+          <t>1405/06/22 - 15:01:44</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1082,7 +1082,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1405/06/22 - 14:54:17</t>
+          <t>1405/06/22 - 14:57:23</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1099,7 +1099,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1405/06/22 - 14:50:48</t>
+          <t>1405/06/22 - 14:54:17</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1116,7 +1116,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1405/06/22 - 14:48:28</t>
+          <t>1405/06/22 - 14:50:48</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1133,15 +1133,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>1405/06/22 - 14:48:28</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ورود به سیستم</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>1405/06/22 - 14:45:00</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>ورود به سیستم</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ورود به سیستم</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
         <is>
           <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>

--- a/Audit_Activity_Log.xlsx
+++ b/Audit_Activity_Log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1405/06/28 - 11:53:48</t>
+          <t>1405/06/28 - 12:11:48</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1405/06/26 - 11:48:02</t>
+          <t>1405/06/28 - 11:53:48</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -470,7 +470,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1405/06/23 - 15:53:52</t>
+          <t>1405/06/26 - 11:48:02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -487,7 +487,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1405/06/23 - 13:14:18</t>
+          <t>1405/06/23 - 15:53:52</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -497,14 +497,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>کاربر [اقای مودب ] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1405/06/23 - 12:58:36</t>
+          <t>1405/06/23 - 13:14:18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -514,65 +514,65 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>کاربر [اقای مودب ] وارد شد.</t>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1405/06/23 - 12:58:14</t>
+          <t>1405/06/23 - 12:58:36</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>خروج</t>
+          <t>ورود به سیستم</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] خارج شد.</t>
+          <t>کاربر [اقای مودب ] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1405/06/23 - 12:58:01</t>
+          <t>1405/06/23 - 12:58:14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>مدیریت کاربران</t>
+          <t>خروج</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>دسترسی‌های کاربر Amin به‌روزرسانی شد.</t>
+          <t>کاربر [مدیرعامل محترم] خارج شد.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1405/06/23 - 12:56:59</t>
+          <t>1405/06/23 - 12:58:01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ورود به سیستم</t>
+          <t>مدیریت کاربران</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>دسترسی‌های کاربر Amin به‌روزرسانی شد.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1405/06/23 - 10:29:08</t>
+          <t>1405/06/23 - 12:56:59</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -589,7 +589,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1405/06/23 - 10:22:35</t>
+          <t>1405/06/23 - 10:29:08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -606,7 +606,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1405/06/23 - 10:03:50</t>
+          <t>1405/06/23 - 10:22:35</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -623,7 +623,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:54:24</t>
+          <t>1405/06/23 - 10:03:50</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -640,7 +640,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:37:17</t>
+          <t>1405/06/23 - 09:54:24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -657,41 +657,41 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:30:32</t>
+          <t>1405/06/23 - 09:37:17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>واحد برش و انبار</t>
+          <t>ورود به سیستم</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>پارت ۱-1 - فندقي  اسلیت شد. طاقه‌ها: 2</t>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:29:47</t>
+          <t>1405/06/23 - 09:30:32</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ورود به سیستم</t>
+          <t>واحد برش و انبار</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>پارت ۱-1 - فندقي  اسلیت شد. طاقه‌ها: 2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:24:06</t>
+          <t>1405/06/23 - 09:29:47</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -708,7 +708,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:14:05</t>
+          <t>1405/06/23 - 09:24:06</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -725,7 +725,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1405/06/23 - 09:10:17</t>
+          <t>1405/06/23 - 09:14:05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -742,7 +742,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1405/06/23 - 08:48:33</t>
+          <t>1405/06/23 - 09:10:17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -759,7 +759,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1405/06/23 - 22:06:41</t>
+          <t>1405/06/23 - 08:48:33</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -776,41 +776,41 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1405/06/23 - 22:05:44</t>
+          <t>1405/06/23 - 22:06:41</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>کارگاه دستگاه 1</t>
+          <t>ورود به سیستم</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>رول مادر با متراژ 2000.0 متر ثبت شد.</t>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1405/06/23 - 22:04:44</t>
+          <t>1405/06/23 - 22:05:44</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ورود به سیستم</t>
+          <t>کارگاه دستگاه 1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>رول مادر با متراژ 2000.0 متر ثبت شد.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1405/06/22 - 21:55:22</t>
+          <t>1405/06/23 - 22:04:44</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -827,7 +827,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1405/06/22 - 21:47:41</t>
+          <t>1405/06/22 - 21:55:22</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -844,7 +844,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1405/06/22 - 17:06:19</t>
+          <t>1405/06/22 - 21:47:41</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -861,7 +861,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:59:10</t>
+          <t>1405/06/22 - 17:06:19</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -878,7 +878,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:52:11</t>
+          <t>1405/06/22 - 16:59:10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -895,7 +895,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:49:08</t>
+          <t>1405/06/22 - 16:52:11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:43:34</t>
+          <t>1405/06/22 - 16:49:08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -929,7 +929,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:32:13</t>
+          <t>1405/06/22 - 16:43:34</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1405/06/22 - 16:03:51</t>
+          <t>1405/06/22 - 16:32:13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -963,7 +963,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:36:36</t>
+          <t>1405/06/22 - 16:03:51</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -980,7 +980,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:30:04</t>
+          <t>1405/06/22 - 15:36:36</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -997,7 +997,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:26:02</t>
+          <t>1405/06/22 - 15:30:04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:18:15</t>
+          <t>1405/06/22 - 15:26:02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1031,41 +1031,41 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:15:07</t>
+          <t>1405/06/22 - 15:18:15</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ثبت سفارش</t>
+          <t>ورود به سیستم</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>فاکتور ۱ برای مشتری مودب  ثبت شد.</t>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:14:25</t>
+          <t>1405/06/22 - 15:15:07</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ورود به سیستم</t>
+          <t>ثبت سفارش</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+          <t>فاکتور ۱ برای مشتری مودب  ثبت شد.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1405/06/22 - 15:01:44</t>
+          <t>1405/06/22 - 15:14:25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1082,7 +1082,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1405/06/22 - 14:57:23</t>
+          <t>1405/06/22 - 15:01:44</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1099,7 +1099,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1405/06/22 - 14:54:17</t>
+          <t>1405/06/22 - 14:57:23</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1116,7 +1116,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1405/06/22 - 14:50:48</t>
+          <t>1405/06/22 - 14:54:17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1133,7 +1133,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1405/06/22 - 14:48:28</t>
+          <t>1405/06/22 - 14:50:48</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1150,15 +1150,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>1405/06/22 - 14:48:28</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ورود به سیستم</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>کاربر [مدیرعامل محترم] وارد شد.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>1405/06/22 - 14:45:00</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>ورود به سیستم</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ورود به سیستم</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
         <is>
           <t>کاربر [مدیرعامل محترم] وارد شد.</t>
         </is>
